--- a/docs/LabPulse Purchasing.xlsx
+++ b/docs/LabPulse Purchasing.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parts" sheetId="1" r:id="R848d799a98ef49b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Earlier choices" sheetId="2" r:id="Rdbc29c93374f4630"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parts" sheetId="1" r:id="R9f369c35fa904ede"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Earlier choices" sheetId="2" r:id="R83104749dffc4429"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -155,8 +155,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CurrentParts" displayName="CurrentParts" ref="A6:K44" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A6:K44"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CurrentParts" displayName="CurrentParts" ref="A6:K46" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A6:K46"/>
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="Category"/>
     <x:tableColumn id="2" name="Part / model"/>
@@ -175,8 +175,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EarlierPurchases" displayName="EarlierPurchases" ref="A6:K11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A6:K11"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EarlierPurchases" displayName="EarlierPurchases" ref="A6:K12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A6:K12"/>
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="Category"/>
     <x:tableColumn id="2" name="Part / model"/>
@@ -525,7 +525,7 @@
         <v>Not specified</v>
       </c>
       <c r="E7" s="12" t="str">
-        <v>Requested; arrival unconfirmed</v>
+        <v>Requested</v>
       </c>
       <c r="F7" s="13" t="str">
         <v>Product page</v>
@@ -536,10 +536,10 @@
         <v>Not recorded</v>
       </c>
       <c r="J7" s="12" t="str">
-        <v>External mains power for the USB hub. Outage fallback remains to be tested.</v>
+        <v>External mains power for the USB hub.</v>
       </c>
       <c r="K7" s="12" t="str">
-        <v>Shopping email supplied 18 Sep 2026</v>
+        <v>Accessory request, 18 Sep 2026</v>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -565,10 +565,10 @@
         <v>Not recorded</v>
       </c>
       <c r="J8" s="12" t="str">
-        <v>For modified Pi SHT40 lead. Exact pack unspecified; match pin spacing and solderable terminals.</v>
+        <v>For modified Pi SHT40 lead. Match pin spacing and use solderable terminals.</v>
       </c>
       <c r="K8" s="12" t="str">
-        <v>Shopping email supplied 18 Sep 2026; cable modification clarification</v>
+        <v>Accessory request, 18 Sep 2026</v>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
@@ -583,7 +583,7 @@
         <v>Not specified</v>
       </c>
       <c r="E9" s="12" t="str">
-        <v>Requested; arrival unconfirmed</v>
+        <v>Requested</v>
       </c>
       <c r="F9" s="13" t="str">
         <v>Product page</v>
@@ -597,7 +597,7 @@
         <v>Pi SHT40 lead. Cut one plug; solder to a single 4-position female header. Not assembled.</v>
       </c>
       <c r="K9" s="12" t="str">
-        <v>Shopping email supplied 18 Sep 2026</v>
+        <v>Accessory request, 18 Sep 2026</v>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
@@ -612,7 +612,7 @@
         <v>Not specified</v>
       </c>
       <c r="E10" s="12" t="str">
-        <v>Requested; arrival unconfirmed</v>
+        <v>Requested</v>
       </c>
       <c r="F10" s="13" t="str">
         <v>Product page</v>
@@ -626,7 +626,7 @@
         <v>SHT40 connection to compressed-air Arduino for main-lab temperature/humidity.</v>
       </c>
       <c r="K10" s="12" t="str">
-        <v>Shopping email supplied 18 Sep 2026</v>
+        <v>Accessory request, 18 Sep 2026</v>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
@@ -641,7 +641,7 @@
         <v>Not specified</v>
       </c>
       <c r="E11" s="12" t="str">
-        <v>Requested; arrival unconfirmed</v>
+        <v>Requested</v>
       </c>
       <c r="F11" s="13" t="str">
         <v>Product page</v>
@@ -655,7 +655,7 @@
         <v>Replace the short supplied display cable. Select 500 mm.</v>
       </c>
       <c r="K11" s="12" t="str">
-        <v>Shopping email supplied 18 Sep 2026</v>
+        <v>Accessory request, 18 Sep 2026</v>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
@@ -670,7 +670,7 @@
         <v>Not specified</v>
       </c>
       <c r="E12" s="12" t="str">
-        <v>Requested; arrival unconfirmed</v>
+        <v>Requested</v>
       </c>
       <c r="F12" s="13" t="str">
         <v>Product page</v>
@@ -684,7 +684,7 @@
         <v>USB power adapter only. The display still needs its DSI cable.</v>
       </c>
       <c r="K12" s="12" t="str">
-        <v>Shopping email supplied 18 Sep 2026</v>
+        <v>Accessory request, 18 Sep 2026</v>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
@@ -701,7 +701,7 @@
         <v>Board capacity</v>
       </c>
       <c r="E13" s="12" t="str">
-        <v>Exact cell model unrecorded</v>
+        <v>Select for X1200</v>
       </c>
       <c r="F13" s="12" t="str">
         <v>Not recorded</v>
@@ -714,7 +714,7 @@
         <v>Not recorded</v>
       </c>
       <c r="J13" s="12" t="str">
-        <v>Two holders. Fitted manufacturer/capacity unrecorded; select cells using X1200 requirements.</v>
+        <v>Two cell holders. Select cells using the X1200 requirements.</v>
       </c>
       <c r="K13" s="12" t="str">
         <v>docs/MAIN_UNIT.md / Parts in the main unit</v>
@@ -750,7 +750,7 @@
         <v>Use the board’s I2C pins. The earlier Qwiic-to-Gravity cable did not fit.</v>
       </c>
       <c r="K14" s="12" t="str">
-        <v>Mini Shopping List.xlsx / Sheet1 row 4; maintainer update 18 Sep 2026</v>
+        <v>Mini Shopping List.xlsx / Sheet1 row 4</v>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
@@ -780,10 +780,10 @@
         <v>Not recorded</v>
       </c>
       <c r="J15" s="12" t="str">
-        <v>Current UPS, confirmed by maintainer. Original UPS HAT (A) price does not apply.</v>
+        <v>Current UPS. Original UPS HAT (A) price does not apply.</v>
       </c>
       <c r="K15" s="12" t="str">
-        <v>LabPulse Sensors.xlsx / Sheet1 row 9; maintainer update 18 Sep 2026</v>
+        <v>LabPulse Sensors.xlsx / Sheet1 row 9</v>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
@@ -912,10 +912,10 @@
         <v>Not recorded</v>
       </c>
       <c r="J19" s="12" t="str">
-        <v>External mains supply selected. Pi/UPS fallback during outages is intended but untested.</v>
+        <v>Use the external 12 V supply. Check USB device power and recovery during commissioning.</v>
       </c>
       <c r="K19" s="12" t="str">
-        <v>docs/MAIN_UNIT.md; August CAD context; maintainer update 18 Sep 2026</v>
+        <v>docs/MAIN_UNIT.md</v>
       </c>
     </row>
     <row r="20" ht="58" customHeight="1">
@@ -948,7 +948,7 @@
         <v>Select 7-inch version. Existing unit has standoffs removed; case printed but not assembled.</v>
       </c>
       <c r="K20" s="12" t="str">
-        <v>Maintainer update 18 Sep 2026; supplier page added for this consolidation</v>
+        <v>docs/MAIN_UNIT.md</v>
       </c>
     </row>
     <row r="21" ht="58" customHeight="1">
@@ -980,10 +980,10 @@
         <v>Listed cost; VAT unknown</v>
       </c>
       <c r="J21" s="12" t="str">
-        <v>Two connections planned: Pi and compressed-air Arduino. Purchased/fitted sensor count is unconfirmed.</v>
+        <v>Connections for the Pi and compressed-air Arduino.</v>
       </c>
       <c r="K21" s="12" t="str">
-        <v>Mini Shopping List.xlsx / Sheet1 row 3; maintainer update 18 Sep 2026</v>
+        <v>Mini Shopping List.xlsx / Sheet1 row 3</v>
       </c>
     </row>
     <row r="22" ht="58" customHeight="1">
@@ -1013,7 +1013,7 @@
         <v>Unit, excl. VAT</v>
       </c>
       <c r="J22" s="12" t="str">
-        <v>Four per pump hub. Eight purchased does not establish that every channel works.</v>
+        <v>Four thermistors per pump hub.</v>
       </c>
       <c r="K22" s="12" t="str">
         <v>Internship purchased items.xlsx / Sheet1 row 6</v>
@@ -1125,7 +1125,7 @@
         <v>Sensors</v>
       </c>
       <c r="B26" s="12" t="str">
-        <v>Triton 1/2 pressure sensors, model unknown</v>
+        <v>Triton 1/2 pressure sensors</v>
       </c>
       <c r="C26" s="14" t="n">
         <v>2</v>
@@ -1189,30 +1189,30 @@
         <v>Cables</v>
       </c>
       <c r="B28" s="12" t="str">
-        <v>40-pin male–female GPIO ribbon, 150 mm</v>
-      </c>
-      <c r="C28" s="14"/>
+        <v>40-pin FPC cable, 0.5 mm pitch, A–B, 25 cm</v>
+      </c>
+      <c r="C28" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="D28" s="12" t="str">
-        <v>Not recorded</v>
+        <v>Per extension assembly</v>
       </c>
       <c r="E28" s="12" t="str">
-        <v>Selected, fitting unconfirmed</v>
+        <v>Selected for enclosure</v>
       </c>
       <c r="F28" s="13" t="str">
         <v>Product page</v>
       </c>
       <c r="G28" s="12" t="str"/>
-      <c r="H28" s="15" t="n">
-        <v>3.5</v>
-      </c>
+      <c r="H28" s="15"/>
       <c r="I28" s="12" t="str">
-        <v>Listed cost; VAT unknown</v>
+        <v>Not recorded</v>
       </c>
       <c r="J28" s="12" t="str">
-        <v>Gertboard-type ribbon for mounting the Gravity board beside the Pi stack.</v>
+        <v>Connects the two adapters across the enclosure. Check pin-1 alignment at both ends.</v>
       </c>
       <c r="K28" s="12" t="str">
-        <v>Mini Shopping List.xlsx / Sheet1 row 6; maintainer update 18 Sep 2026</v>
+        <v>docs/MAIN_UNIT.md / GPIO extension across the enclosure</v>
       </c>
     </row>
     <row r="29" ht="58" customHeight="1">
@@ -1220,32 +1220,30 @@
         <v>Cables</v>
       </c>
       <c r="B29" s="12" t="str">
-        <v>DC extension lead, 1.5 m, 2.5 mm</v>
+        <v>40-pin FPC to right-angle 2x20 IDC male plug adapter</v>
       </c>
       <c r="C29" s="14" t="n">
         <v>1</v>
       </c>
       <c r="D29" s="12" t="str">
-        <v>Purchased quantity</v>
+        <v>Per extension assembly</v>
       </c>
       <c r="E29" s="12" t="str">
-        <v>Purchased record</v>
+        <v>Selected for enclosure</v>
       </c>
       <c r="F29" s="13" t="str">
         <v>Product page</v>
       </c>
       <c r="G29" s="12" t="str"/>
-      <c r="H29" s="15" t="n">
-        <v>1.79</v>
-      </c>
+      <c r="H29" s="15"/>
       <c r="I29" s="12" t="str">
-        <v>Unit, excl. VAT</v>
+        <v>Not recorded</v>
       </c>
       <c r="J29" s="12" t="str">
-        <v>Historical lead. Do not assume it fits the newer 2.1 mm hub supply.</v>
+        <v>Expansion-board end: plug fits the Gravity GPIO connector.</v>
       </c>
       <c r="K29" s="12" t="str">
-        <v>Internship purchased items.xlsx / Sheet1 row 16</v>
+        <v>docs/MAIN_UNIT.md / GPIO extension across the enclosure</v>
       </c>
     </row>
     <row r="30" ht="58" customHeight="1">
@@ -1253,32 +1251,30 @@
         <v>Cables</v>
       </c>
       <c r="B30" s="12" t="str">
-        <v>USB-A to USB-B cable, 3 m</v>
+        <v>40-pin FPC to straight 2x20 IDC female socket adapter</v>
       </c>
       <c r="C30" s="14" t="n">
         <v>1</v>
       </c>
       <c r="D30" s="12" t="str">
-        <v>Purchased quantity</v>
+        <v>Per extension assembly</v>
       </c>
       <c r="E30" s="12" t="str">
-        <v>Purchased record</v>
+        <v>Selected for enclosure</v>
       </c>
       <c r="F30" s="13" t="str">
         <v>Product page</v>
       </c>
       <c r="G30" s="12" t="str"/>
-      <c r="H30" s="15" t="n">
-        <v>1.74</v>
-      </c>
+      <c r="H30" s="15"/>
       <c r="I30" s="12" t="str">
-        <v>Unit, excl. VAT</v>
+        <v>Not recorded</v>
       </c>
       <c r="J30" s="12" t="str">
-        <v>Arduino-to-hub connection.</v>
+        <v>Pi end: socket fits the Pi GPIO header.</v>
       </c>
       <c r="K30" s="12" t="str">
-        <v>Internship purchased items.xlsx / Sheet1 row 14</v>
+        <v>docs/MAIN_UNIT.md / GPIO extension across the enclosure</v>
       </c>
     </row>
     <row r="31" ht="58" customHeight="1">
@@ -1286,10 +1282,10 @@
         <v>Cables</v>
       </c>
       <c r="B31" s="12" t="str">
-        <v>USB-A to USB-B cable, 5 m</v>
+        <v>DC extension lead, 1.5 m, 2.5 mm</v>
       </c>
       <c r="C31" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" s="12" t="str">
         <v>Purchased quantity</v>
@@ -1302,27 +1298,27 @@
       </c>
       <c r="G31" s="12" t="str"/>
       <c r="H31" s="15" t="n">
-        <v>2.53</v>
+        <v>1.79</v>
       </c>
       <c r="I31" s="12" t="str">
         <v>Unit, excl. VAT</v>
       </c>
       <c r="J31" s="12" t="str">
-        <v>Arduino-to-hub connections.</v>
+        <v>Historical lead. Do not assume it fits the newer 2.1 mm hub supply.</v>
       </c>
       <c r="K31" s="12" t="str">
-        <v>Internship purchased items.xlsx / Sheet1 row 15</v>
+        <v>Internship purchased items.xlsx / Sheet1 row 16</v>
       </c>
     </row>
     <row r="32" ht="58" customHeight="1">
       <c r="A32" s="12" t="str">
-        <v>Connectors</v>
+        <v>Cables</v>
       </c>
       <c r="B32" s="12" t="str">
-        <v>GE-1337 connectors, RS 8011017</v>
+        <v>USB-A to USB-B cable, 3 m</v>
       </c>
       <c r="C32" s="14" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D32" s="12" t="str">
         <v>Purchased quantity</v>
@@ -1335,27 +1331,27 @@
       </c>
       <c r="G32" s="12" t="str"/>
       <c r="H32" s="15" t="n">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="I32" s="12" t="str">
         <v>Unit, excl. VAT</v>
       </c>
       <c r="J32" s="12" t="str">
-        <v>Connectors for the recorded thermistors.</v>
+        <v>Arduino-to-hub connection.</v>
       </c>
       <c r="K32" s="12" t="str">
-        <v>Internship purchased items.xlsx / Sheet1 row 7</v>
+        <v>Internship purchased items.xlsx / Sheet1 row 14</v>
       </c>
     </row>
     <row r="33" ht="58" customHeight="1">
       <c r="A33" s="12" t="str">
-        <v>Connectors</v>
+        <v>Cables</v>
       </c>
       <c r="B33" s="12" t="str">
-        <v>Raspberry Pi GPIO riser header</v>
+        <v>USB-A to USB-B cable, 5 m</v>
       </c>
       <c r="C33" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" s="12" t="str">
         <v>Purchased quantity</v>
@@ -1368,30 +1364,30 @@
       </c>
       <c r="G33" s="12" t="str"/>
       <c r="H33" s="15" t="n">
-        <v>0.8</v>
+        <v>2.53</v>
       </c>
       <c r="I33" s="12" t="str">
         <v>Unit, excl. VAT</v>
       </c>
       <c r="J33" s="12" t="str">
-        <v>Original purchase. Confirm required stack clearance.</v>
+        <v>Arduino-to-hub connections.</v>
       </c>
       <c r="K33" s="12" t="str">
-        <v>Internship purchased items.xlsx / Sheet1 row 9</v>
+        <v>Internship purchased items.xlsx / Sheet1 row 15</v>
       </c>
     </row>
     <row r="34" ht="58" customHeight="1">
       <c r="A34" s="12" t="str">
-        <v>Mounting</v>
+        <v>Connectors</v>
       </c>
       <c r="B34" s="12" t="str">
-        <v>M2.5 nylon standoff pack</v>
+        <v>GE-1337 connectors, RS 8011017</v>
       </c>
       <c r="C34" s="14" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D34" s="12" t="str">
-        <v>Purchased packs</v>
+        <v>Purchased quantity</v>
       </c>
       <c r="E34" s="12" t="str">
         <v>Purchased record</v>
@@ -1401,45 +1397,49 @@
       </c>
       <c r="G34" s="12" t="str"/>
       <c r="H34" s="15" t="n">
-        <v>0.58</v>
+        <v>1.58</v>
       </c>
       <c r="I34" s="12" t="str">
         <v>Unit, excl. VAT</v>
       </c>
       <c r="J34" s="12" t="str">
-        <v>Quantity is packs, not individual standoffs.</v>
+        <v>Connectors for the recorded thermistors.</v>
       </c>
       <c r="K34" s="12" t="str">
-        <v>Internship purchased items.xlsx / Sheet1 row 10</v>
+        <v>Internship purchased items.xlsx / Sheet1 row 7</v>
       </c>
     </row>
     <row r="35" ht="58" customHeight="1">
       <c r="A35" s="12" t="str">
-        <v>Mounting</v>
+        <v>Connectors</v>
       </c>
       <c r="B35" s="12" t="str">
-        <v>Wurth 970160155 M2.5 standoff</v>
-      </c>
-      <c r="C35" s="14"/>
+        <v>Raspberry Pi GPIO riser header</v>
+      </c>
+      <c r="C35" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="D35" s="12" t="str">
-        <v>Not recorded</v>
+        <v>Purchased quantity</v>
       </c>
       <c r="E35" s="12" t="str">
-        <v>Recorded in build context</v>
-      </c>
-      <c r="F35" s="12" t="str">
-        <v>Not recorded</v>
+        <v>Purchased record</v>
+      </c>
+      <c r="F35" s="13" t="str">
+        <v>Product page</v>
       </c>
       <c r="G35" s="12" t="str"/>
-      <c r="H35" s="15"/>
+      <c r="H35" s="15" t="n">
+        <v>0.8</v>
+      </c>
       <c r="I35" s="12" t="str">
-        <v>Not recorded</v>
+        <v>Unit, excl. VAT</v>
       </c>
       <c r="J35" s="12" t="str">
-        <v>Female–female, 16 mm. Exact purchase link not supplied; do not substitute male–female 971160151.</v>
+        <v>Original purchase. Confirm required stack clearance.</v>
       </c>
       <c r="K35" s="12" t="str">
-        <v>docs/MAIN_UNIT.md / July CAD context</v>
+        <v>Internship purchased items.xlsx / Sheet1 row 9</v>
       </c>
     </row>
     <row r="36" ht="58" customHeight="1">
@@ -1447,13 +1447,13 @@
         <v>Mounting</v>
       </c>
       <c r="B36" s="12" t="str">
-        <v>Wurth 971160151 M2.5 standoff</v>
+        <v>M2.5 nylon standoff pack</v>
       </c>
       <c r="C36" s="14" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D36" s="12" t="str">
-        <v>Purchased quantity</v>
+        <v>Purchased packs</v>
       </c>
       <c r="E36" s="12" t="str">
         <v>Purchased record</v>
@@ -1463,60 +1463,54 @@
       </c>
       <c r="G36" s="12" t="str"/>
       <c r="H36" s="15" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="I36" s="12" t="str">
         <v>Unit, excl. VAT</v>
       </c>
       <c r="J36" s="12" t="str">
-        <v>Male–female, 16 mm. Distinct from female–female 970160155.</v>
+        <v>Quantity is packs, not individual standoffs.</v>
       </c>
       <c r="K36" s="12" t="str">
-        <v>Internship purchased items.xlsx / Sheet1 row 8</v>
+        <v>Internship purchased items.xlsx / Sheet1 row 10</v>
       </c>
     </row>
     <row r="37" ht="58" customHeight="1">
       <c r="A37" s="12" t="str">
-        <v>Plumbing</v>
+        <v>Mounting</v>
       </c>
       <c r="B37" s="12" t="str">
-        <v>1/2-inch thread washer</v>
-      </c>
-      <c r="C37" s="14" t="n">
-        <v>8</v>
-      </c>
+        <v>Wurth 970160155 M2.5 standoff</v>
+      </c>
+      <c r="C37" s="14"/>
       <c r="D37" s="12" t="str">
-        <v>Purchased quantity</v>
+        <v>Not recorded</v>
       </c>
       <c r="E37" s="12" t="str">
-        <v>Purchased record</v>
-      </c>
-      <c r="F37" s="13" t="str">
-        <v>Product page</v>
+        <v>Mounting component</v>
+      </c>
+      <c r="F37" s="12" t="str">
+        <v>Not recorded</v>
       </c>
       <c r="G37" s="12" t="str"/>
-      <c r="H37" s="15" t="n">
-        <v>0.48</v>
-      </c>
+      <c r="H37" s="15"/>
       <c r="I37" s="12" t="str">
-        <v>Unit, excl. VAT</v>
+        <v>Not recorded</v>
       </c>
       <c r="J37" s="12" t="str">
-        <v>Installation-specific plumbing.</v>
-      </c>
-      <c r="K37" s="12" t="str">
-        <v>Internship purchased items.xlsx / Sheet1 row 18</v>
-      </c>
+        <v>Female–female, 16 mm. Match the fixing to the assembly.</v>
+      </c>
+      <c r="K37" s="12" t="str"/>
     </row>
     <row r="38" ht="58" customHeight="1">
       <c r="A38" s="12" t="str">
-        <v>Plumbing</v>
+        <v>Mounting</v>
       </c>
       <c r="B38" s="12" t="str">
-        <v>22 mm x 1/2-inch female coupler</v>
+        <v>Wurth 971160151 M2.5 standoff</v>
       </c>
       <c r="C38" s="14" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D38" s="12" t="str">
         <v>Purchased quantity</v>
@@ -1529,16 +1523,16 @@
       </c>
       <c r="G38" s="12" t="str"/>
       <c r="H38" s="15" t="n">
-        <v>3.408333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="I38" s="12" t="str">
         <v>Unit, excl. VAT</v>
       </c>
       <c r="J38" s="12" t="str">
-        <v>Flomasta brass compression adapting coupler.</v>
+        <v>Male–female, 16 mm. Distinct from female–female 970160155.</v>
       </c>
       <c r="K38" s="12" t="str">
-        <v>Internship purchased items.xlsx / Sheet1 row 21</v>
+        <v>Internship purchased items.xlsx / Sheet1 row 8</v>
       </c>
     </row>
     <row r="39" ht="58" customHeight="1">
@@ -1546,13 +1540,13 @@
         <v>Plumbing</v>
       </c>
       <c r="B39" s="12" t="str">
-        <v>Bonded seal washer (Dowty)</v>
+        <v>1/2-inch thread washer</v>
       </c>
       <c r="C39" s="14" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D39" s="12" t="str">
-        <v>Purchased packs</v>
+        <v>Purchased quantity</v>
       </c>
       <c r="E39" s="12" t="str">
         <v>Purchased record</v>
@@ -1562,16 +1556,16 @@
       </c>
       <c r="G39" s="12" t="str"/>
       <c r="H39" s="15" t="n">
-        <v>6.658333333333334</v>
+        <v>0.48</v>
       </c>
       <c r="I39" s="12" t="str">
         <v>Unit, excl. VAT</v>
       </c>
       <c r="J39" s="12" t="str">
-        <v>Original listed pack quantity. Confirm thread size and pack contents before ordering.</v>
+        <v>Installation-specific plumbing.</v>
       </c>
       <c r="K39" s="12" t="str">
-        <v>Internship purchased items.xlsx / Sheet1 row 17</v>
+        <v>Internship purchased items.xlsx / Sheet1 row 18</v>
       </c>
     </row>
     <row r="40" ht="58" customHeight="1">
@@ -1579,7 +1573,7 @@
         <v>Plumbing</v>
       </c>
       <c r="B40" s="12" t="str">
-        <v>BSPT male-thread hose tail</v>
+        <v>22 mm x 1/2-inch female coupler</v>
       </c>
       <c r="C40" s="14" t="n">
         <v>4</v>
@@ -1595,16 +1589,16 @@
       </c>
       <c r="G40" s="12" t="str"/>
       <c r="H40" s="15" t="n">
-        <v>3.88</v>
+        <v>3.408333333333333</v>
       </c>
       <c r="I40" s="12" t="str">
         <v>Unit, excl. VAT</v>
       </c>
       <c r="J40" s="12" t="str">
-        <v>Supplier family link. Exact size is not recorded.</v>
+        <v>Flomasta brass compression adapting coupler.</v>
       </c>
       <c r="K40" s="12" t="str">
-        <v>Internship purchased items.xlsx / Sheet1 row 22</v>
+        <v>Internship purchased items.xlsx / Sheet1 row 21</v>
       </c>
     </row>
     <row r="41" ht="58" customHeight="1">
@@ -1612,13 +1606,13 @@
         <v>Plumbing</v>
       </c>
       <c r="B41" s="12" t="str">
-        <v>Female G to G 90-degree elbow</v>
+        <v>Bonded seal washer (Dowty)</v>
       </c>
       <c r="C41" s="14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D41" s="12" t="str">
-        <v>Purchased quantity</v>
+        <v>Purchased packs</v>
       </c>
       <c r="E41" s="12" t="str">
         <v>Purchased record</v>
@@ -1628,16 +1622,16 @@
       </c>
       <c r="G41" s="12" t="str"/>
       <c r="H41" s="15" t="n">
-        <v>5.22</v>
+        <v>6.658333333333334</v>
       </c>
       <c r="I41" s="12" t="str">
         <v>Unit, excl. VAT</v>
       </c>
       <c r="J41" s="12" t="str">
-        <v>RS 4992953. Confirm thread and pressure rating against the circuit.</v>
+        <v>Original listed pack quantity. Confirm thread size and pack contents before ordering.</v>
       </c>
       <c r="K41" s="12" t="str">
-        <v>Internship purchased items.xlsx / Sheet1 row 20</v>
+        <v>Internship purchased items.xlsx / Sheet1 row 17</v>
       </c>
     </row>
     <row r="42" ht="58" customHeight="1">
@@ -1645,10 +1639,10 @@
         <v>Plumbing</v>
       </c>
       <c r="B42" s="12" t="str">
-        <v>Male R to R 1/2-inch fitting</v>
+        <v>BSPT male-thread hose tail</v>
       </c>
       <c r="C42" s="14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D42" s="12" t="str">
         <v>Purchased quantity</v>
@@ -1661,16 +1655,16 @@
       </c>
       <c r="G42" s="12" t="str"/>
       <c r="H42" s="15" t="n">
-        <v>4.99</v>
+        <v>3.88</v>
       </c>
       <c r="I42" s="12" t="str">
         <v>Unit, excl. VAT</v>
       </c>
       <c r="J42" s="12" t="str">
-        <v>RS 4993041. Confirm thread and pressure rating against the circuit.</v>
+        <v>Supplier family link. Exact size is not recorded.</v>
       </c>
       <c r="K42" s="12" t="str">
-        <v>Internship purchased items.xlsx / Sheet1 row 19</v>
+        <v>Internship purchased items.xlsx / Sheet1 row 22</v>
       </c>
     </row>
     <row r="43" ht="58" customHeight="1">
@@ -1678,10 +1672,10 @@
         <v>Plumbing</v>
       </c>
       <c r="B43" s="12" t="str">
-        <v>Stainless steel T fitting</v>
+        <v>Female G to G 90-degree elbow</v>
       </c>
       <c r="C43" s="14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D43" s="12" t="str">
         <v>Purchased quantity</v>
@@ -1694,51 +1688,117 @@
       </c>
       <c r="G43" s="12" t="str"/>
       <c r="H43" s="15" t="n">
-        <v>6.53</v>
+        <v>5.22</v>
       </c>
       <c r="I43" s="12" t="str">
         <v>Unit, excl. VAT</v>
       </c>
       <c r="J43" s="12" t="str">
-        <v>RS 4992981. Confirm size and rating against the circuit.</v>
+        <v>RS 4992953. Confirm thread and pressure rating against the circuit.</v>
       </c>
       <c r="K43" s="12" t="str">
-        <v>Internship purchased items.xlsx / Sheet1 row 23</v>
+        <v>Internship purchased items.xlsx / Sheet1 row 20</v>
       </c>
     </row>
     <row r="44" ht="58" customHeight="1">
       <c r="A44" s="12" t="str">
+        <v>Plumbing</v>
+      </c>
+      <c r="B44" s="12" t="str">
+        <v>Male R to R 1/2-inch fitting</v>
+      </c>
+      <c r="C44" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="D44" s="12" t="str">
+        <v>Purchased quantity</v>
+      </c>
+      <c r="E44" s="12" t="str">
+        <v>Purchased record</v>
+      </c>
+      <c r="F44" s="13" t="str">
+        <v>Product page</v>
+      </c>
+      <c r="G44" s="12" t="str"/>
+      <c r="H44" s="15" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="I44" s="12" t="str">
+        <v>Unit, excl. VAT</v>
+      </c>
+      <c r="J44" s="12" t="str">
+        <v>RS 4993041. Confirm thread and pressure rating against the circuit.</v>
+      </c>
+      <c r="K44" s="12" t="str">
+        <v>Internship purchased items.xlsx / Sheet1 row 19</v>
+      </c>
+    </row>
+    <row r="45" ht="58" customHeight="1">
+      <c r="A45" s="12" t="str">
+        <v>Plumbing</v>
+      </c>
+      <c r="B45" s="12" t="str">
+        <v>Stainless steel T fitting</v>
+      </c>
+      <c r="C45" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="D45" s="12" t="str">
+        <v>Purchased quantity</v>
+      </c>
+      <c r="E45" s="12" t="str">
+        <v>Purchased record</v>
+      </c>
+      <c r="F45" s="13" t="str">
+        <v>Product page</v>
+      </c>
+      <c r="G45" s="12" t="str"/>
+      <c r="H45" s="15" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="I45" s="12" t="str">
+        <v>Unit, excl. VAT</v>
+      </c>
+      <c r="J45" s="12" t="str">
+        <v>RS 4992981. Confirm size and rating against the circuit.</v>
+      </c>
+      <c r="K45" s="12" t="str">
+        <v>Internship purchased items.xlsx / Sheet1 row 23</v>
+      </c>
+    </row>
+    <row r="46" ht="58" customHeight="1">
+      <c r="A46" s="12" t="str">
         <v>Enclosure</v>
       </c>
-      <c r="B44" s="12" t="str">
+      <c r="B46" s="12" t="str">
         <v>Custom printed main-unit case</v>
       </c>
-      <c r="C44" s="14" t="n">
+      <c r="C46" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="D44" s="12" t="str">
+      <c r="D46" s="12" t="str">
         <v>One case described</v>
       </c>
-      <c r="E44" s="12" t="str">
+      <c r="E46" s="12" t="str">
         <v>Printed; assembly pending</v>
       </c>
-      <c r="F44" s="12" t="str">
-        <v>Not recorded</v>
-      </c>
-      <c r="G44" s="12" t="str"/>
-      <c r="H44" s="15"/>
-      <c r="I44" s="12" t="str">
-        <v>Not recorded</v>
-      </c>
-      <c r="J44" s="12" t="str">
-        <v>Waiting for key parts. No finished manufacturing package recorded.</v>
-      </c>
-      <c r="K44" s="12" t="str">
-        <v>Maintainer update 18 Sep 2026; docs/MAIN_UNIT.md</v>
+      <c r="F46" s="12" t="str">
+        <v>Not recorded</v>
+      </c>
+      <c r="G46" s="12" t="str"/>
+      <c r="H46" s="15"/>
+      <c r="I46" s="12" t="str">
+        <v>Not recorded</v>
+      </c>
+      <c r="J46" s="12" t="str">
+        <v>Printed; awaiting parts for assembly.</v>
+      </c>
+      <c r="K46" s="12" t="str">
+        <v>docs/MAIN_UNIT.md</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E7:E44">
+  <conditionalFormatting sqref="E7:E46">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="unconfirmed"/>
     <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="needed"/>
   </conditionalFormatting>
@@ -1776,18 +1836,20 @@
     <hyperlink ref="F32" r:id="purchaseLinkF32"/>
     <hyperlink ref="F33" r:id="purchaseLinkF33"/>
     <hyperlink ref="F34" r:id="purchaseLinkF34"/>
+    <hyperlink ref="F35" r:id="purchaseLinkF35"/>
     <hyperlink ref="F36" r:id="purchaseLinkF36"/>
-    <hyperlink ref="F37" r:id="purchaseLinkF37"/>
     <hyperlink ref="F38" r:id="purchaseLinkF38"/>
     <hyperlink ref="F39" r:id="purchaseLinkF39"/>
     <hyperlink ref="F40" r:id="purchaseLinkF40"/>
     <hyperlink ref="F41" r:id="purchaseLinkF41"/>
     <hyperlink ref="F42" r:id="purchaseLinkF42"/>
     <hyperlink ref="F43" r:id="purchaseLinkF43"/>
+    <hyperlink ref="F44" r:id="purchaseLinkF44"/>
+    <hyperlink ref="F45" r:id="purchaseLinkF45"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="R8ffbc8084fca4844"/>
+    <tablePart r:id="R2a9bea40997b417d"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1925,30 +1987,30 @@
         <v>Superseded</v>
       </c>
       <c r="B7" s="12" t="str">
-        <v>DHT11 formerly connected to Pi</v>
-      </c>
-      <c r="C7" s="14" t="n">
-        <v>1</v>
-      </c>
+        <v>40-pin male–female GPIO ribbon, 150 mm</v>
+      </c>
+      <c r="C7" s="14"/>
       <c r="D7" s="12" t="str">
-        <v>Historical inventory</v>
+        <v>Not recorded</v>
       </c>
       <c r="E7" s="12" t="str">
-        <v>Earlier installation</v>
+        <v>Earlier choice</v>
       </c>
       <c r="F7" s="13" t="str">
         <v>Product page</v>
       </c>
       <c r="G7" s="12" t="str"/>
-      <c r="H7" s="15"/>
+      <c r="H7" s="15" t="n">
+        <v>3.5</v>
+      </c>
       <c r="I7" s="12" t="str">
-        <v>Not recorded</v>
+        <v>Listed cost; VAT unknown</v>
       </c>
       <c r="J7" s="12" t="str">
-        <v>Pi room sensor planned to change to SHT40. Old Working status is not a current verification.</v>
+        <v>Replaced by the 25 cm FPC cable and two header adapters for reach and flexibility across the enclosure.</v>
       </c>
       <c r="K7" s="12" t="str">
-        <v>LabPulse Sensors.xlsx / Sheet1 row 8; docs/HARDWARE.md</v>
+        <v>Mini Shopping List.xlsx / Sheet1 row 6</v>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -1956,94 +2018,94 @@
         <v>Superseded</v>
       </c>
       <c r="B8" s="12" t="str">
-        <v>Gembird UHB-U2P4-04 USB hub</v>
+        <v>DHT11 formerly connected to Pi</v>
       </c>
       <c r="C8" s="14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D8" s="12" t="str">
-        <v>Purchased quantity</v>
+        <v>Historical inventory</v>
       </c>
       <c r="E8" s="12" t="str">
-        <v>Earlier purchase</v>
+        <v>Earlier installation</v>
       </c>
       <c r="F8" s="13" t="str">
         <v>Product page</v>
       </c>
       <c r="G8" s="12" t="str"/>
-      <c r="H8" s="15" t="n">
-        <v>5.25</v>
-      </c>
+      <c r="H8" s="15"/>
       <c r="I8" s="12" t="str">
-        <v>Unit, excl. VAT</v>
+        <v>Not recorded</v>
       </c>
       <c r="J8" s="12" t="str">
-        <v>Earlier USB hubs. Current main-unit plan uses the Waveshare 2IN–4OUT hub.</v>
+        <v>Replaced in the Pi configuration by SHT40.</v>
       </c>
       <c r="K8" s="12" t="str">
-        <v>Internship purchased items.xlsx / Sheet1 row 24</v>
+        <v>LabPulse Sensors.xlsx / Sheet1 row 8; docs/HARDWARE.md</v>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="12" t="str">
-        <v>Earlier choice</v>
+        <v>Superseded</v>
       </c>
       <c r="B9" s="12" t="str">
-        <v>Industrial USB 3.2 hub (earlier list)</v>
-      </c>
-      <c r="C9" s="14"/>
+        <v>Gembird UHB-U2P4-04 USB hub</v>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="D9" s="12" t="str">
-        <v>Not recorded</v>
+        <v>Purchased quantity</v>
       </c>
       <c r="E9" s="12" t="str">
-        <v>Earlier candidate</v>
+        <v>Earlier purchase</v>
       </c>
       <c r="F9" s="13" t="str">
         <v>Product page</v>
       </c>
       <c r="G9" s="12" t="str"/>
       <c r="H9" s="15" t="n">
-        <v>21.2</v>
+        <v>5.25</v>
       </c>
       <c r="I9" s="12" t="str">
-        <v>Listed cost; VAT unknown</v>
+        <v>Unit, excl. VAT</v>
       </c>
       <c r="J9" s="12" t="str">
-        <v>Exact match to the owned Waveshare 2IN–4OUT hub is unconfirmed. Keep the original supplier link.</v>
+        <v>Earlier USB hubs. Current main-unit plan uses the Waveshare 2IN–4OUT hub.</v>
       </c>
       <c r="K9" s="12" t="str">
-        <v>Mini Shopping List.xlsx / Sheet1 row 2; maintainer update 18 Sep 2026</v>
+        <v>Internship purchased items.xlsx / Sheet1 row 24</v>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="12" t="str">
-        <v>Superseded</v>
+        <v>Earlier choice</v>
       </c>
       <c r="B10" s="12" t="str">
-        <v>Qwiic-to-Gravity JST-SH/JST-PH cable</v>
+        <v>Industrial USB 3.2 hub (earlier list)</v>
       </c>
       <c r="C10" s="14"/>
       <c r="D10" s="12" t="str">
         <v>Not recorded</v>
       </c>
       <c r="E10" s="12" t="str">
-        <v>Incompatible choice</v>
+        <v>Earlier candidate</v>
       </c>
       <c r="F10" s="13" t="str">
         <v>Product page</v>
       </c>
       <c r="G10" s="12" t="str"/>
       <c r="H10" s="15" t="n">
-        <v>1.2</v>
+        <v>21.2</v>
       </c>
       <c r="I10" s="12" t="str">
         <v>Listed cost; VAT unknown</v>
       </c>
       <c r="J10" s="12" t="str">
-        <v>Do not reorder for this connection. Replaced by the planned modified JST-SH cable and female header.</v>
+        <v>Earlier industrial hub selection. See Parts for the Waveshare 2IN–4OUT hub.</v>
       </c>
       <c r="K10" s="12" t="str">
-        <v>Mini Shopping List.xlsx / Sheet1 row 5; maintainer update 18 Sep 2026</v>
+        <v>Mini Shopping List.xlsx / Sheet1 row 2</v>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
@@ -2051,36 +2113,67 @@
         <v>Superseded</v>
       </c>
       <c r="B11" s="12" t="str">
-        <v>Waveshare UPS HAT (A)</v>
-      </c>
-      <c r="C11" s="14" t="n">
-        <v>1</v>
-      </c>
+        <v>Qwiic-to-Gravity JST-SH/JST-PH cable</v>
+      </c>
+      <c r="C11" s="14"/>
       <c r="D11" s="12" t="str">
-        <v>Purchased quantity</v>
+        <v>Not recorded</v>
       </c>
       <c r="E11" s="12" t="str">
-        <v>Superseded</v>
+        <v>Incompatible choice</v>
       </c>
       <c r="F11" s="13" t="str">
         <v>Product page</v>
       </c>
       <c r="G11" s="12" t="str"/>
       <c r="H11" s="15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I11" s="12" t="str">
+        <v>Listed cost; VAT unknown</v>
+      </c>
+      <c r="J11" s="12" t="str">
+        <v>Do not reorder for this connection. Replaced by the planned modified JST-SH cable and female header.</v>
+      </c>
+      <c r="K11" s="12" t="str">
+        <v>Mini Shopping List.xlsx / Sheet1 row 5</v>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="12" t="str">
+        <v>Superseded</v>
+      </c>
+      <c r="B12" s="12" t="str">
+        <v>Waveshare UPS HAT (A)</v>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="12" t="str">
+        <v>Purchased quantity</v>
+      </c>
+      <c r="E12" s="12" t="str">
+        <v>Superseded</v>
+      </c>
+      <c r="F12" s="13" t="str">
+        <v>Product page</v>
+      </c>
+      <c r="G12" s="12" t="str"/>
+      <c r="H12" s="15" t="n">
         <v>19.75</v>
       </c>
-      <c r="I11" s="12" t="str">
-        <v>Unit, excl. VAT</v>
-      </c>
-      <c r="J11" s="12" t="str">
+      <c r="I12" s="12" t="str">
+        <v>Unit, excl. VAT</v>
+      </c>
+      <c r="J12" s="12" t="str">
         <v>DO NOT REORDER for the current unit. Replaced by X1200.</v>
       </c>
-      <c r="K11" s="12" t="str">
+      <c r="K12" s="12" t="str">
         <v>Internship purchased items.xlsx / Sheet1 row 12</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E7:E11">
+  <conditionalFormatting sqref="E7:E12">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="unconfirmed"/>
     <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="needed"/>
   </conditionalFormatting>
@@ -2090,10 +2183,11 @@
     <hyperlink ref="F9" r:id="purchaseLinkF9"/>
     <hyperlink ref="F10" r:id="purchaseLinkF10"/>
     <hyperlink ref="F11" r:id="purchaseLinkF11"/>
+    <hyperlink ref="F12" r:id="purchaseLinkF12"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="R262535129ab3424f"/>
+    <tablePart r:id="Rb8285b2a63584b0f"/>
   </tableParts>
 </worksheet>
 </file>